--- a/docs/demo-data/GNDEC_CSE_3rd_4th_year_demo_teachers_blank.xlsx
+++ b/docs/demo-data/GNDEC_CSE_3rd_4th_year_demo_teachers_blank.xlsx
@@ -3470,7 +3470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Student AA</t>
+          <t>Aarav Sharma</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Student AB</t>
+          <t>Aanya Dhillon</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Student AC</t>
+          <t>Arjun Mehta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Student AD</t>
+          <t>Bhavya Kohli</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3578,7 +3578,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Student AE</t>
+          <t>Gurpreet Arora</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Student AF</t>
+          <t>Diya Bedi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Student AG</t>
+          <t>Harjot Saini</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Student AH</t>
+          <t>Gurleen Mann</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Student AI</t>
+          <t>Karan Grewal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Student AJ</t>
+          <t>Harleen Kapoor</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Student AK</t>
+          <t>Manav Brar</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Student AL</t>
+          <t>Ishita Sandhu</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Student AM</t>
+          <t>Navdeep Malhotra</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Student AN</t>
+          <t>Jasleen Goyal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Student AO</t>
+          <t>Rohan Thind</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Student AP</t>
+          <t>Kritika Bansal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Student AQ</t>
+          <t>Sahil Sethi</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Student AR</t>
+          <t>Mehak Walia</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Student AS</t>
+          <t>Tejas Gill</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Student AT</t>
+          <t>Navneet Sidhu</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Student AU</t>
+          <t>Varun Jain</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Student AV</t>
+          <t>Prabhleen Ahuja</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Student AW</t>
+          <t>Yuvraj Verma</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Student AX</t>
+          <t>Riya Chopra</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Student AY</t>
+          <t>Aman Bhatia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Student AZ</t>
+          <t>Sanya Sharma</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Student AAA</t>
+          <t>Daksh Dhillon</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Student AAB</t>
+          <t>Tanvi Mehta</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Student AAC</t>
+          <t>Ishaan Kohli</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Student AAD</t>
+          <t>Avneet Arora</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Student AAE</t>
+          <t>Jaskaran Bedi</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4307,7 +4307,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Student AAF</t>
+          <t>Simran Saini</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Student AAG</t>
+          <t>Kabir Mann</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Student AAH</t>
+          <t>Komal Grewal</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Student AAI</t>
+          <t>Lakshay Kapoor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Student AAJ</t>
+          <t>Muskan Brar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Student AAK</t>
+          <t>Parth Sandhu</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4469,7 +4469,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Student AAL</t>
+          <t>Nidhi Malhotra</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Student AAM</t>
+          <t>Ravneet Goyal</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4523,7 +4523,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Student AAN</t>
+          <t>Pooja Thind</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Student AAO</t>
+          <t>Simranjeet Bansal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Student AAP</t>
+          <t>Ritika Sethi</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Student BA</t>
+          <t>Tanish Walia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Student BB</t>
+          <t>Shreya Gill</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Student BC</t>
+          <t>Uday Sidhu</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Student BD</t>
+          <t>Tanya Jain</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Student BE</t>
+          <t>Vikram Ahuja</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4739,7 +4739,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Student BF</t>
+          <t>Vanshika Verma</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Student BG</t>
+          <t>Arshdeep Chopra</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4793,7 +4793,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Student BH</t>
+          <t>Anjali Bhatia</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Student BI</t>
+          <t>Bhavik Sharma</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Student BJ</t>
+          <t>Divya Dhillon</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Student BK</t>
+          <t>Dev Mehta</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Student BL</t>
+          <t>Ekam Kohli</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4928,7 +4928,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Student BM</t>
+          <t>Gagandeep Arora</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4955,7 +4955,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Student BN</t>
+          <t>Gunjan Bedi</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Student BO</t>
+          <t>Hardik Saini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Student BP</t>
+          <t>Jasmeet Mann</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Student BQ</t>
+          <t>Inderjeet Grewal</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Student BR</t>
+          <t>Manpreet Kapoor</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Student BS</t>
+          <t>Aarav Kohli</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Student BT</t>
+          <t>Aanya Arora</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Student BU</t>
+          <t>Arjun Bedi</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Student BV</t>
+          <t>Bhavya Saini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Student BW</t>
+          <t>Gurpreet Mann</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Student BX</t>
+          <t>Diya Grewal</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5252,7 +5252,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Student BY</t>
+          <t>Harjot Kapoor</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Student BZ</t>
+          <t>Gurleen Brar</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Student BAA</t>
+          <t>Karan Sandhu</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Student BAB</t>
+          <t>Harleen Malhotra</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Student BAC</t>
+          <t>Manav Goyal</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Student BAD</t>
+          <t>Ishita Thind</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Student BAE</t>
+          <t>Navdeep Bansal</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Student BAF</t>
+          <t>Jasleen Sethi</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Student BAG</t>
+          <t>Rohan Walia</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Student BAH</t>
+          <t>Kritika Gill</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Student BAI</t>
+          <t>Sahil Sidhu</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Student BAJ</t>
+          <t>Mehak Jain</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Student BAK</t>
+          <t>Tejas Ahuja</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5603,7 +5603,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Student BAL</t>
+          <t>Navneet Verma</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5630,7 +5630,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Student BAM</t>
+          <t>Varun Chopra</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Student BAN</t>
+          <t>Prabhleen Bhatia</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Student BAO</t>
+          <t>Yuvraj Sharma</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Student BAP</t>
+          <t>Riya Dhillon</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Student CA</t>
+          <t>Aman Mehta</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5765,7 +5765,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Student CB</t>
+          <t>Sanya Kohli</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Student CC</t>
+          <t>Daksh Arora</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Student CD</t>
+          <t>Tanvi Bedi</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Student CE</t>
+          <t>Ishaan Saini</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Student CF</t>
+          <t>Avneet Mann</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Student CG</t>
+          <t>Jaskaran Grewal</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5927,7 +5927,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Student CH</t>
+          <t>Simran Kapoor</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Student CI</t>
+          <t>Kabir Brar</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Student CJ</t>
+          <t>Komal Sandhu</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Student CK</t>
+          <t>Lakshay Malhotra</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6035,7 +6035,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Student CL</t>
+          <t>Muskan Goyal</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Student CM</t>
+          <t>Parth Thind</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Student CN</t>
+          <t>Nidhi Bansal</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Student CO</t>
+          <t>Ravneet Sethi</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Student CP</t>
+          <t>Pooja Walia</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Student CQ</t>
+          <t>Simranjeet Gill</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Student CR</t>
+          <t>Ritika Sidhu</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Student CS</t>
+          <t>Tanish Jain</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Student CT</t>
+          <t>Shreya Ahuja</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Student CU</t>
+          <t>Uday Verma</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Student CV</t>
+          <t>Tanya Chopra</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Student CW</t>
+          <t>Vikram Bhatia</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Student CX</t>
+          <t>Vanshika Sharma</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Student CY</t>
+          <t>Arshdeep Dhillon</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Student CZ</t>
+          <t>Anjali Mehta</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Student CAA</t>
+          <t>Bhavik Kohli</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Student CAB</t>
+          <t>Divya Arora</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Student CAC</t>
+          <t>Dev Bedi</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Student CAD</t>
+          <t>Ekam Saini</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Student CAE</t>
+          <t>Gagandeep Mann</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Student CAF</t>
+          <t>Gunjan Grewal</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -6602,7 +6602,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Student CAG</t>
+          <t>Hardik Kapoor</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Student CAH</t>
+          <t>Jasmeet Brar</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Student CAI</t>
+          <t>Inderjeet Sandhu</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Student CAJ</t>
+          <t>Manpreet Malhotra</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Student CAK</t>
+          <t>Aarav Saini</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Student CAL</t>
+          <t>Aanya Mann</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Student CAM</t>
+          <t>Arjun Grewal</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Student CAN</t>
+          <t>Bhavya Kapoor</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Student CAO</t>
+          <t>Gurpreet Brar</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Student AA</t>
+          <t>Diya Sandhu</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Student AB</t>
+          <t>Harjot Malhotra</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Student AC</t>
+          <t>Gurleen Goyal</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Student AD</t>
+          <t>Karan Thind</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -6953,7 +6953,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Student AE</t>
+          <t>Harleen Bansal</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Student AF</t>
+          <t>Manav Sethi</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Student AG</t>
+          <t>Ishita Walia</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Student AH</t>
+          <t>Navdeep Gill</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Student AI</t>
+          <t>Jasleen Sidhu</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Student AJ</t>
+          <t>Rohan Jain</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Student AK</t>
+          <t>Kritika Ahuja</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Student AL</t>
+          <t>Sahil Verma</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Student AM</t>
+          <t>Mehak Chopra</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Student AN</t>
+          <t>Tejas Bhatia</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Student AO</t>
+          <t>Navneet Sharma</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Student AP</t>
+          <t>Varun Dhillon</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -7277,7 +7277,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Student AQ</t>
+          <t>Prabhleen Mehta</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Student AR</t>
+          <t>Yuvraj Kohli</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Student AS</t>
+          <t>Riya Arora</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Student AT</t>
+          <t>Aman Bedi</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Student AU</t>
+          <t>Sanya Saini</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Student AV</t>
+          <t>Daksh Mann</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -7439,7 +7439,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Student AW</t>
+          <t>Tanvi Grewal</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Student AX</t>
+          <t>Ishaan Kapoor</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Student AY</t>
+          <t>Avneet Brar</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -7520,7 +7520,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Student AZ</t>
+          <t>Jaskaran Sandhu</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Student AAA</t>
+          <t>Simran Malhotra</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Student AAB</t>
+          <t>Kabir Goyal</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Student AAC</t>
+          <t>Komal Thind</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -7628,7 +7628,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Student AAD</t>
+          <t>Lakshay Bansal</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -7655,7 +7655,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Student AAE</t>
+          <t>Muskan Sethi</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -7682,7 +7682,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Student AAF</t>
+          <t>Parth Walia</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Student AAG</t>
+          <t>Nidhi Gill</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Student AAH</t>
+          <t>Ravneet Sidhu</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Student AAI</t>
+          <t>Pooja Jain</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -7790,7 +7790,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Student AAJ</t>
+          <t>Simranjeet Ahuja</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -7817,7 +7817,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Student AAK</t>
+          <t>Ritika Verma</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Student AAL</t>
+          <t>Tanish Chopra</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Student AAM</t>
+          <t>Shreya Bhatia</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Student AAN</t>
+          <t>Uday Sharma</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Student AAO</t>
+          <t>Tanya Dhillon</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -7952,7 +7952,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Student AAP</t>
+          <t>Vikram Mehta</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -7979,7 +7979,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Student BA</t>
+          <t>Vanshika Kohli</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -8006,7 +8006,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Student BB</t>
+          <t>Arshdeep Arora</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Student BC</t>
+          <t>Anjali Bedi</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Student BD</t>
+          <t>Bhavik Saini</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -8087,7 +8087,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Student BE</t>
+          <t>Divya Mann</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Student BF</t>
+          <t>Dev Grewal</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Student BG</t>
+          <t>Ekam Kapoor</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Student BH</t>
+          <t>Gagandeep Brar</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Student BI</t>
+          <t>Gunjan Sandhu</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Student BJ</t>
+          <t>Hardik Malhotra</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Student BK</t>
+          <t>Jasmeet Goyal</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Student BL</t>
+          <t>Inderjeet Thind</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Student BM</t>
+          <t>Manpreet Bansal</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Student BN</t>
+          <t>Aarav Kapoor</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Student BO</t>
+          <t>Aanya Brar</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -8384,7 +8384,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Student BP</t>
+          <t>Arjun Sandhu</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Student BQ</t>
+          <t>Bhavya Malhotra</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -8438,7 +8438,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Student BR</t>
+          <t>Gurpreet Goyal</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -8465,7 +8465,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Student BS</t>
+          <t>Diya Thind</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Student BT</t>
+          <t>Harjot Bansal</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -8519,7 +8519,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Student BU</t>
+          <t>Gurleen Sethi</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -8546,7 +8546,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Student BV</t>
+          <t>Karan Walia</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Student BW</t>
+          <t>Harleen Gill</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Student BX</t>
+          <t>Manav Sidhu</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Student BY</t>
+          <t>Ishita Jain</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Student BZ</t>
+          <t>Navdeep Ahuja</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Student BAA</t>
+          <t>Jasleen Verma</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Student BAB</t>
+          <t>Rohan Chopra</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Student BAC</t>
+          <t>Kritika Bhatia</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -8762,7 +8762,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Student BAD</t>
+          <t>Sahil Sharma</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Student BAE</t>
+          <t>Mehak Dhillon</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Student BAF</t>
+          <t>Tejas Mehta</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -8843,7 +8843,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Student BAG</t>
+          <t>Navneet Kohli</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -8870,7 +8870,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Student BAH</t>
+          <t>Varun Arora</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Student BAI</t>
+          <t>Prabhleen Bedi</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Student BAJ</t>
+          <t>Yuvraj Saini</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Student BAK</t>
+          <t>Riya Mann</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -8978,7 +8978,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Student BAL</t>
+          <t>Aman Grewal</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Student BAM</t>
+          <t>Sanya Kapoor</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Student BAN</t>
+          <t>Daksh Brar</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -9059,7 +9059,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Student BAO</t>
+          <t>Tanvi Sandhu</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -9086,7 +9086,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Student BAP</t>
+          <t>Ishaan Malhotra</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Student CA</t>
+          <t>Avneet Goyal</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Student CB</t>
+          <t>Jaskaran Thind</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Student CC</t>
+          <t>Simran Bansal</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Student CD</t>
+          <t>Kabir Sethi</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Student CE</t>
+          <t>Komal Walia</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -9248,7 +9248,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Student CF</t>
+          <t>Lakshay Gill</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Student CG</t>
+          <t>Muskan Sidhu</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -9302,7 +9302,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Student CH</t>
+          <t>Parth Jain</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -9329,7 +9329,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Student CI</t>
+          <t>Nidhi Ahuja</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Student CJ</t>
+          <t>Ravneet Verma</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -9383,7 +9383,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Student CK</t>
+          <t>Pooja Chopra</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Student CL</t>
+          <t>Simranjeet Bhatia</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Student CM</t>
+          <t>Ritika Sharma</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Student CN</t>
+          <t>Tanish Dhillon</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Student CO</t>
+          <t>Shreya Mehta</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Student CP</t>
+          <t>Uday Kohli</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Student CQ</t>
+          <t>Tanya Arora</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Student CR</t>
+          <t>Vikram Bedi</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Student CS</t>
+          <t>Vanshika Saini</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Student CT</t>
+          <t>Arshdeep Mann</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -9653,7 +9653,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Student CU</t>
+          <t>Anjali Grewal</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Student CV</t>
+          <t>Bhavik Kapoor</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Student CW</t>
+          <t>Divya Brar</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -9734,7 +9734,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Student CX</t>
+          <t>Dev Sandhu</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Student CY</t>
+          <t>Ekam Malhotra</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Student CZ</t>
+          <t>Gagandeep Goyal</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Student CAA</t>
+          <t>Gunjan Thind</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Student CAB</t>
+          <t>Hardik Bansal</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Student CAC</t>
+          <t>Jasmeet Sethi</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Student CAD</t>
+          <t>Inderjeet Walia</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Student CAE</t>
+          <t>Manpreet Gill</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Student CAF</t>
+          <t>Aarav Malhotra</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Student CAG</t>
+          <t>Aanya Goyal</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Student CAH</t>
+          <t>Arjun Thind</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Student CAI</t>
+          <t>Bhavya Bansal</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Student CAJ</t>
+          <t>Gurpreet Sethi</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Student CAK</t>
+          <t>Diya Walia</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Student CAL</t>
+          <t>Harjot Gill</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Student CAM</t>
+          <t>Gurleen Sidhu</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Student CAN</t>
+          <t>Karan Jain</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Student CAO</t>
+          <t>Harleen Ahuja</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
